--- a/business_forms/049_unsuccessful_trade_evaluation_form--business_forms.xlsx
+++ b/business_forms/049_unsuccessful_trade_evaluation_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Action Status</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Follow Up Status</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>review_by</t>
+          <t>review_by_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>review_status_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Review Status 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>submitted_by_user</t>
+          <t>submitted_by_user_2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Submitted By User</t>
+          <t>Submitted By User 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>review_status_choices</t>
+          <t>review_status_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>review_status_choices</t>
+          <t>review_status_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>review_status_choices</t>
+          <t>review_status_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
